--- a/data/b2_primavera/B2 Primavera 12-2025.xlsx
+++ b/data/b2_primavera/B2 Primavera 12-2025.xlsx
@@ -4986,20 +4986,20 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1523.93</v>
+        <v>1842.97</v>
       </c>
     </row>
     <row r="3">
@@ -5017,43 +5017,43 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>56947.39</v>
+        <v>57887.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>45998</v>
+        <v>45997</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>4073.94</v>
+        <v>1345.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46001</v>
+        <v>45998</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>14000</v>
+        <v>4111.79</v>
       </c>
     </row>
     <row r="6">
@@ -5062,70 +5062,70 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3600</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46003</v>
+        <v>46001</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1131.93</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46003</v>
+        <v>46002</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1038.46</v>
+        <v>2130.21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46005</v>
+        <v>46003</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1687.28</v>
+        <v>1085.32</v>
       </c>
     </row>
     <row r="10">
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>3956.24</v>
+        <v>3979.87</v>
       </c>
     </row>
     <row r="11">
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>8836.299999999999</v>
+        <v>9823.09</v>
       </c>
     </row>
     <row r="12">
@@ -5179,43 +5179,43 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1846.97</v>
+        <v>1420.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46007</v>
+        <v>46011</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>1409.86</v>
+        <v>19777.22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46010</v>
+        <v>46011</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1142.81</v>
+        <v>2456.53</v>
       </c>
     </row>
     <row r="15">
@@ -5224,16 +5224,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>20342.32</v>
+        <v>1408.77</v>
       </c>
     </row>
     <row r="16">
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>4258.43</v>
+        <v>4241.63</v>
       </c>
     </row>
     <row r="17">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>4201.21</v>
+        <v>4372.55</v>
       </c>
     </row>
     <row r="18">
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>1680.99</v>
+        <v>1714</v>
       </c>
     </row>
   </sheetData>
